--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V6.0.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V6.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356303F7-F753-486F-AD2D-6B03BA1AC564}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31DD190-9D19-4CF4-9F2B-AD0F71CCDA50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="18" xr2:uid="{B7614390-11AA-4CA0-8D0B-42C45BC335B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="17" xr2:uid="{B7614390-11AA-4CA0-8D0B-42C45BC335B4}"/>
   </bookViews>
   <sheets>
     <sheet name="문서 개요" sheetId="7" r:id="rId1"/>
@@ -4708,12 +4708,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4722,6 +4716,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5596,13 +5596,13 @@
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="156" t="s">
+      <c r="B22" s="159" t="s">
         <v>706</v>
       </c>
-      <c r="C22" s="156"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="156"/>
+      <c r="C22" s="159"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="159"/>
     </row>
     <row r="24" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A24" s="14" t="s">
@@ -5612,13 +5612,13 @@
     </row>
     <row r="25" spans="1:6" ht="164.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="14"/>
-      <c r="B25" s="156" t="s">
+      <c r="B25" s="159" t="s">
         <v>707</v>
       </c>
-      <c r="C25" s="156"/>
-      <c r="D25" s="156"/>
-      <c r="E25" s="156"/>
-      <c r="F25" s="156"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C26" s="100"/>
@@ -5634,99 +5634,99 @@
     </row>
     <row r="28" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="14"/>
-      <c r="B28" s="156" t="s">
+      <c r="B28" s="159" t="s">
         <v>689</v>
       </c>
-      <c r="C28" s="156"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="157" t="s">
+      <c r="C28" s="159"/>
+      <c r="D28" s="159"/>
+      <c r="E28" s="160" t="s">
         <v>691</v>
       </c>
-      <c r="F28" s="157"/>
+      <c r="F28" s="160"/>
     </row>
     <row r="29" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="14"/>
-      <c r="B29" s="156" t="s">
+      <c r="B29" s="159" t="s">
         <v>690</v>
       </c>
-      <c r="C29" s="156"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="157" t="s">
+      <c r="C29" s="159"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="160" t="s">
         <v>692</v>
       </c>
-      <c r="F29" s="157"/>
+      <c r="F29" s="160"/>
     </row>
     <row r="30" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="14"/>
-      <c r="B30" s="156" t="s">
+      <c r="B30" s="159" t="s">
         <v>699</v>
       </c>
-      <c r="C30" s="156"/>
-      <c r="D30" s="156"/>
-      <c r="E30" s="157" t="s">
+      <c r="C30" s="159"/>
+      <c r="D30" s="159"/>
+      <c r="E30" s="160" t="s">
         <v>693</v>
       </c>
-      <c r="F30" s="157"/>
+      <c r="F30" s="160"/>
     </row>
     <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="14"/>
-      <c r="B31" s="156" t="s">
+      <c r="B31" s="159" t="s">
         <v>700</v>
       </c>
-      <c r="C31" s="156"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="157" t="s">
+      <c r="C31" s="159"/>
+      <c r="D31" s="159"/>
+      <c r="E31" s="160" t="s">
         <v>694</v>
       </c>
-      <c r="F31" s="157"/>
+      <c r="F31" s="160"/>
     </row>
     <row r="32" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="14"/>
-      <c r="B32" s="156" t="s">
+      <c r="B32" s="159" t="s">
         <v>701</v>
       </c>
-      <c r="C32" s="156"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="157" t="s">
+      <c r="C32" s="159"/>
+      <c r="D32" s="159"/>
+      <c r="E32" s="160" t="s">
         <v>695</v>
       </c>
-      <c r="F32" s="157"/>
+      <c r="F32" s="160"/>
     </row>
     <row r="33" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="14"/>
-      <c r="B33" s="156" t="s">
+      <c r="B33" s="159" t="s">
         <v>702</v>
       </c>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="157" t="s">
+      <c r="C33" s="159"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="160" t="s">
         <v>696</v>
       </c>
-      <c r="F33" s="157"/>
+      <c r="F33" s="160"/>
     </row>
     <row r="34" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="14"/>
-      <c r="B34" s="156" t="s">
+      <c r="B34" s="159" t="s">
         <v>703</v>
       </c>
-      <c r="C34" s="156"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="157" t="s">
+      <c r="C34" s="159"/>
+      <c r="D34" s="159"/>
+      <c r="E34" s="160" t="s">
         <v>697</v>
       </c>
-      <c r="F34" s="157"/>
+      <c r="F34" s="160"/>
     </row>
     <row r="35" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="14"/>
-      <c r="B35" s="156" t="s">
+      <c r="B35" s="159" t="s">
         <v>704</v>
       </c>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="157" t="s">
+      <c r="C35" s="159"/>
+      <c r="D35" s="159"/>
+      <c r="E35" s="160" t="s">
         <v>698</v>
       </c>
-      <c r="F35" s="157"/>
+      <c r="F35" s="160"/>
     </row>
     <row r="37" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A37" s="14" t="s">
@@ -5735,16 +5735,19 @@
       <c r="B37" s="14"/>
     </row>
     <row r="38" spans="1:6" ht="95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="158" t="s">
+      <c r="B38" s="156" t="s">
         <v>705</v>
       </c>
-      <c r="C38" s="159"/>
-      <c r="D38" s="159"/>
-      <c r="E38" s="159"/>
-      <c r="F38" s="160"/>
+      <c r="C38" s="157"/>
+      <c r="D38" s="157"/>
+      <c r="E38" s="157"/>
+      <c r="F38" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B25:F25"/>
@@ -5761,9 +5764,6 @@
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -8383,16 +8383,16 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="125.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="159" t="s">
         <v>600</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C4" s="100"/>
@@ -8409,16 +8409,16 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="252" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="156" t="s">
+      <c r="B6" s="159" t="s">
         <v>478</v>
       </c>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="159"/>
     </row>
     <row r="8" spans="1:15" ht="36" x14ac:dyDescent="0.45">
       <c r="A8" s="86" t="s">
@@ -12793,7 +12793,7 @@
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="15.58203125" customWidth="1"/>
     <col min="5" max="5" width="33.4140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="6" max="6" width="54.6640625" customWidth="1"/>
     <col min="7" max="12" width="15.58203125" customWidth="1"/>
     <col min="13" max="13" width="37.75" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="44.9140625" bestFit="1" customWidth="1"/>
@@ -14478,35 +14478,33 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="O27" s="155"/>
+      <c r="O27" s="155">
+        <v>0.3</v>
+      </c>
       <c r="P27" s="155"/>
-      <c r="Q27" s="155" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="Q27" s="155">
+        <v>0.3</v>
       </c>
       <c r="R27" s="155" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="S27" s="155" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="S27" s="155">
+        <v>0.3</v>
       </c>
       <c r="T27" s="155" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="U27" s="155" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="U27" s="155">
+        <v>0.3</v>
       </c>
       <c r="V27" s="155" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W27" s="155" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="W27" s="155">
+        <v>0.3</v>
       </c>
       <c r="X27" s="155" t="str">
         <f t="shared" si="7"/>
@@ -14734,39 +14732,43 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="O31" s="155"/>
-      <c r="P31" s="155"/>
-      <c r="Q31" s="155" t="str">
+      <c r="O31" s="155">
+        <v>0.1</v>
+      </c>
+      <c r="P31" s="155">
+        <v>0.1</v>
+      </c>
+      <c r="Q31" s="155">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="R31" s="155" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="R31" s="155">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="S31" s="155" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="S31" s="155">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T31" s="155" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="T31" s="155">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="U31" s="155" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="U31" s="155">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="V31" s="155" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="V31" s="155">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W31" s="155" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="W31" s="155">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="X31" s="155" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="X31" s="155">
         <f t="shared" si="7"/>
-        <v/>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
@@ -14862,35 +14864,37 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="O33" s="155"/>
+      <c r="O33" s="155">
+        <v>0.2</v>
+      </c>
       <c r="P33" s="155"/>
-      <c r="Q33" s="155" t="str">
+      <c r="Q33" s="155">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="R33" s="155" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="S33" s="155" t="str">
+      <c r="S33" s="155">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="T33" s="155" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="U33" s="155" t="str">
+      <c r="U33" s="155">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="V33" s="155" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W33" s="155" t="str">
+      <c r="W33" s="155">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="X33" s="155" t="str">
         <f t="shared" si="7"/>
@@ -17632,11 +17636,11 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="123.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="159" t="s">
         <v>519</v>
       </c>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
@@ -17644,11 +17648,11 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="121.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="156" t="s">
+      <c r="B7" s="159" t="s">
         <v>521</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
     </row>
     <row r="9" spans="1:11" ht="36" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
@@ -17869,15 +17873,15 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="198" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="159" t="s">
         <v>588</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
       <c r="I3" s="20"/>
     </row>
     <row r="5" spans="1:9" ht="36" x14ac:dyDescent="0.45">
@@ -17886,15 +17890,15 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="260" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="156" t="s">
+      <c r="B6" s="159" t="s">
         <v>513</v>
       </c>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
       <c r="I6" s="20"/>
     </row>
     <row r="8" spans="1:9" ht="36" x14ac:dyDescent="0.45">
@@ -17904,15 +17908,15 @@
     </row>
     <row r="9" spans="1:9" ht="145.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14"/>
-      <c r="B9" s="156" t="s">
+      <c r="B9" s="159" t="s">
         <v>684</v>
       </c>
-      <c r="C9" s="156"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="159"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B11" s="97" t="s">
@@ -18030,15 +18034,15 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="305.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="156" t="s">
+      <c r="B22" s="159" t="s">
         <v>535</v>
       </c>
-      <c r="C22" s="156"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="156"/>
-      <c r="G22" s="156"/>
-      <c r="H22" s="156"/>
+      <c r="C22" s="159"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="159"/>
+      <c r="G22" s="159"/>
+      <c r="H22" s="159"/>
       <c r="I22" s="20"/>
     </row>
     <row r="24" spans="1:19" ht="36" x14ac:dyDescent="0.45">
@@ -24893,15 +24897,15 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="321" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="159" t="s">
         <v>589</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V6.0.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V6.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31DD190-9D19-4CF4-9F2B-AD0F71CCDA50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5403AA53-68B2-47D3-8FBE-8D6CC4927E80}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="17" xr2:uid="{B7614390-11AA-4CA0-8D0B-42C45BC335B4}"/>
   </bookViews>
@@ -4708,6 +4708,12 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4716,12 +4722,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5596,13 +5596,13 @@
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="159" t="s">
+      <c r="B22" s="157" t="s">
         <v>706</v>
       </c>
-      <c r="C22" s="159"/>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="159"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
     </row>
     <row r="24" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A24" s="14" t="s">
@@ -5612,13 +5612,13 @@
     </row>
     <row r="25" spans="1:6" ht="164.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="14"/>
-      <c r="B25" s="159" t="s">
+      <c r="B25" s="157" t="s">
         <v>707</v>
       </c>
-      <c r="C25" s="159"/>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
+      <c r="C25" s="157"/>
+      <c r="D25" s="157"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C26" s="100"/>
@@ -5634,99 +5634,99 @@
     </row>
     <row r="28" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="14"/>
-      <c r="B28" s="159" t="s">
+      <c r="B28" s="157" t="s">
         <v>689</v>
       </c>
-      <c r="C28" s="159"/>
-      <c r="D28" s="159"/>
-      <c r="E28" s="160" t="s">
+      <c r="C28" s="157"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="156" t="s">
         <v>691</v>
       </c>
-      <c r="F28" s="160"/>
+      <c r="F28" s="156"/>
     </row>
     <row r="29" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="14"/>
-      <c r="B29" s="159" t="s">
+      <c r="B29" s="157" t="s">
         <v>690</v>
       </c>
-      <c r="C29" s="159"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="160" t="s">
+      <c r="C29" s="157"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="156" t="s">
         <v>692</v>
       </c>
-      <c r="F29" s="160"/>
+      <c r="F29" s="156"/>
     </row>
     <row r="30" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="14"/>
-      <c r="B30" s="159" t="s">
+      <c r="B30" s="157" t="s">
         <v>699</v>
       </c>
-      <c r="C30" s="159"/>
-      <c r="D30" s="159"/>
-      <c r="E30" s="160" t="s">
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="156" t="s">
         <v>693</v>
       </c>
-      <c r="F30" s="160"/>
+      <c r="F30" s="156"/>
     </row>
     <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="14"/>
-      <c r="B31" s="159" t="s">
+      <c r="B31" s="157" t="s">
         <v>700</v>
       </c>
-      <c r="C31" s="159"/>
-      <c r="D31" s="159"/>
-      <c r="E31" s="160" t="s">
+      <c r="C31" s="157"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="156" t="s">
         <v>694</v>
       </c>
-      <c r="F31" s="160"/>
+      <c r="F31" s="156"/>
     </row>
     <row r="32" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="14"/>
-      <c r="B32" s="159" t="s">
+      <c r="B32" s="157" t="s">
         <v>701</v>
       </c>
-      <c r="C32" s="159"/>
-      <c r="D32" s="159"/>
-      <c r="E32" s="160" t="s">
+      <c r="C32" s="157"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="156" t="s">
         <v>695</v>
       </c>
-      <c r="F32" s="160"/>
+      <c r="F32" s="156"/>
     </row>
     <row r="33" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="14"/>
-      <c r="B33" s="159" t="s">
+      <c r="B33" s="157" t="s">
         <v>702</v>
       </c>
-      <c r="C33" s="159"/>
-      <c r="D33" s="159"/>
-      <c r="E33" s="160" t="s">
+      <c r="C33" s="157"/>
+      <c r="D33" s="157"/>
+      <c r="E33" s="156" t="s">
         <v>696</v>
       </c>
-      <c r="F33" s="160"/>
+      <c r="F33" s="156"/>
     </row>
     <row r="34" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="14"/>
-      <c r="B34" s="159" t="s">
+      <c r="B34" s="157" t="s">
         <v>703</v>
       </c>
-      <c r="C34" s="159"/>
-      <c r="D34" s="159"/>
-      <c r="E34" s="160" t="s">
+      <c r="C34" s="157"/>
+      <c r="D34" s="157"/>
+      <c r="E34" s="156" t="s">
         <v>697</v>
       </c>
-      <c r="F34" s="160"/>
+      <c r="F34" s="156"/>
     </row>
     <row r="35" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="14"/>
-      <c r="B35" s="159" t="s">
+      <c r="B35" s="157" t="s">
         <v>704</v>
       </c>
-      <c r="C35" s="159"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="160" t="s">
+      <c r="C35" s="157"/>
+      <c r="D35" s="157"/>
+      <c r="E35" s="156" t="s">
         <v>698</v>
       </c>
-      <c r="F35" s="160"/>
+      <c r="F35" s="156"/>
     </row>
     <row r="37" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A37" s="14" t="s">
@@ -5735,16 +5735,19 @@
       <c r="B37" s="14"/>
     </row>
     <row r="38" spans="1:6" ht="95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="156" t="s">
+      <c r="B38" s="158" t="s">
         <v>705</v>
       </c>
-      <c r="C38" s="157"/>
-      <c r="D38" s="157"/>
-      <c r="E38" s="157"/>
-      <c r="F38" s="158"/>
+      <c r="C38" s="159"/>
+      <c r="D38" s="159"/>
+      <c r="E38" s="159"/>
+      <c r="F38" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E34:F34"/>
@@ -5761,9 +5764,6 @@
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B35:D35"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -8383,16 +8383,16 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="125.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="159" t="s">
+      <c r="B3" s="157" t="s">
         <v>600</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C4" s="100"/>
@@ -8409,16 +8409,16 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="252" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="159" t="s">
+      <c r="B6" s="157" t="s">
         <v>478</v>
       </c>
-      <c r="C6" s="159"/>
-      <c r="D6" s="159"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="159"/>
-      <c r="I6" s="159"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="157"/>
     </row>
     <row r="8" spans="1:15" ht="36" x14ac:dyDescent="0.45">
       <c r="A8" s="86" t="s">
@@ -14475,6 +14475,12 @@
       <c r="H27">
         <v>1</v>
       </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
       <c r="K27">
         <v>0</v>
       </c>
@@ -14599,6 +14605,12 @@
         <v>0</v>
       </c>
       <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
         <v>1</v>
       </c>
       <c r="K29">
@@ -14727,6 +14739,12 @@
         <v>0</v>
       </c>
       <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
         <v>1</v>
       </c>
       <c r="K31">
@@ -17636,11 +17654,11 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="123.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="159" t="s">
+      <c r="B4" s="157" t="s">
         <v>519</v>
       </c>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="157"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
@@ -17648,11 +17666,11 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="121.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="159" t="s">
+      <c r="B7" s="157" t="s">
         <v>521</v>
       </c>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
     </row>
     <row r="9" spans="1:11" ht="36" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
@@ -17873,15 +17891,15 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="198" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="159" t="s">
+      <c r="B3" s="157" t="s">
         <v>588</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
       <c r="I3" s="20"/>
     </row>
     <row r="5" spans="1:9" ht="36" x14ac:dyDescent="0.45">
@@ -17890,15 +17908,15 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="260" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="159" t="s">
+      <c r="B6" s="157" t="s">
         <v>513</v>
       </c>
-      <c r="C6" s="159"/>
-      <c r="D6" s="159"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="159"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
       <c r="I6" s="20"/>
     </row>
     <row r="8" spans="1:9" ht="36" x14ac:dyDescent="0.45">
@@ -17908,15 +17926,15 @@
     </row>
     <row r="9" spans="1:9" ht="145.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14"/>
-      <c r="B9" s="159" t="s">
+      <c r="B9" s="157" t="s">
         <v>684</v>
       </c>
-      <c r="C9" s="159"/>
-      <c r="D9" s="159"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="159"/>
-      <c r="G9" s="159"/>
-      <c r="H9" s="159"/>
+      <c r="C9" s="157"/>
+      <c r="D9" s="157"/>
+      <c r="E9" s="157"/>
+      <c r="F9" s="157"/>
+      <c r="G9" s="157"/>
+      <c r="H9" s="157"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B11" s="97" t="s">
@@ -18034,15 +18052,15 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="305.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="159" t="s">
+      <c r="B22" s="157" t="s">
         <v>535</v>
       </c>
-      <c r="C22" s="159"/>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="159"/>
-      <c r="G22" s="159"/>
-      <c r="H22" s="159"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="157"/>
       <c r="I22" s="20"/>
     </row>
     <row r="24" spans="1:19" ht="36" x14ac:dyDescent="0.45">
@@ -24897,15 +24915,15 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="321" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="159" t="s">
+      <c r="B3" s="157" t="s">
         <v>589</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V6.0.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 전투 데이터 테이블 V6.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5403AA53-68B2-47D3-8FBE-8D6CC4927E80}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46903E8-CB9E-4568-ADF4-FAEF2D5C4223}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="17" xr2:uid="{B7614390-11AA-4CA0-8D0B-42C45BC335B4}"/>
   </bookViews>
@@ -4708,11 +4708,11 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5596,13 +5596,13 @@
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="157" t="s">
+      <c r="B22" s="156" t="s">
         <v>706</v>
       </c>
-      <c r="C22" s="157"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="156"/>
     </row>
     <row r="24" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A24" s="14" t="s">
@@ -5612,13 +5612,13 @@
     </row>
     <row r="25" spans="1:6" ht="164.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="14"/>
-      <c r="B25" s="157" t="s">
+      <c r="B25" s="156" t="s">
         <v>707</v>
       </c>
-      <c r="C25" s="157"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
-      <c r="F25" s="157"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="156"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C26" s="100"/>
@@ -5634,99 +5634,99 @@
     </row>
     <row r="28" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="14"/>
-      <c r="B28" s="157" t="s">
+      <c r="B28" s="156" t="s">
         <v>689</v>
       </c>
-      <c r="C28" s="157"/>
-      <c r="D28" s="157"/>
-      <c r="E28" s="156" t="s">
+      <c r="C28" s="156"/>
+      <c r="D28" s="156"/>
+      <c r="E28" s="157" t="s">
         <v>691</v>
       </c>
-      <c r="F28" s="156"/>
+      <c r="F28" s="157"/>
     </row>
     <row r="29" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="14"/>
-      <c r="B29" s="157" t="s">
+      <c r="B29" s="156" t="s">
         <v>690</v>
       </c>
-      <c r="C29" s="157"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="156" t="s">
+      <c r="C29" s="156"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="157" t="s">
         <v>692</v>
       </c>
-      <c r="F29" s="156"/>
+      <c r="F29" s="157"/>
     </row>
     <row r="30" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="14"/>
-      <c r="B30" s="157" t="s">
+      <c r="B30" s="156" t="s">
         <v>699</v>
       </c>
-      <c r="C30" s="157"/>
-      <c r="D30" s="157"/>
-      <c r="E30" s="156" t="s">
+      <c r="C30" s="156"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="157" t="s">
         <v>693</v>
       </c>
-      <c r="F30" s="156"/>
+      <c r="F30" s="157"/>
     </row>
     <row r="31" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="14"/>
-      <c r="B31" s="157" t="s">
+      <c r="B31" s="156" t="s">
         <v>700</v>
       </c>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="156" t="s">
+      <c r="C31" s="156"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="157" t="s">
         <v>694</v>
       </c>
-      <c r="F31" s="156"/>
+      <c r="F31" s="157"/>
     </row>
     <row r="32" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="14"/>
-      <c r="B32" s="157" t="s">
+      <c r="B32" s="156" t="s">
         <v>701</v>
       </c>
-      <c r="C32" s="157"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="156" t="s">
+      <c r="C32" s="156"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="157" t="s">
         <v>695</v>
       </c>
-      <c r="F32" s="156"/>
+      <c r="F32" s="157"/>
     </row>
     <row r="33" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="14"/>
-      <c r="B33" s="157" t="s">
+      <c r="B33" s="156" t="s">
         <v>702</v>
       </c>
-      <c r="C33" s="157"/>
-      <c r="D33" s="157"/>
-      <c r="E33" s="156" t="s">
+      <c r="C33" s="156"/>
+      <c r="D33" s="156"/>
+      <c r="E33" s="157" t="s">
         <v>696</v>
       </c>
-      <c r="F33" s="156"/>
+      <c r="F33" s="157"/>
     </row>
     <row r="34" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="14"/>
-      <c r="B34" s="157" t="s">
+      <c r="B34" s="156" t="s">
         <v>703</v>
       </c>
-      <c r="C34" s="157"/>
-      <c r="D34" s="157"/>
-      <c r="E34" s="156" t="s">
+      <c r="C34" s="156"/>
+      <c r="D34" s="156"/>
+      <c r="E34" s="157" t="s">
         <v>697</v>
       </c>
-      <c r="F34" s="156"/>
+      <c r="F34" s="157"/>
     </row>
     <row r="35" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="14"/>
-      <c r="B35" s="157" t="s">
+      <c r="B35" s="156" t="s">
         <v>704</v>
       </c>
-      <c r="C35" s="157"/>
-      <c r="D35" s="157"/>
-      <c r="E35" s="156" t="s">
+      <c r="C35" s="156"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="157" t="s">
         <v>698</v>
       </c>
-      <c r="F35" s="156"/>
+      <c r="F35" s="157"/>
     </row>
     <row r="37" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A37" s="14" t="s">
@@ -5745,12 +5745,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B25:F25"/>
@@ -5764,6 +5758,12 @@
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -8383,16 +8383,16 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="125.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="156" t="s">
         <v>600</v>
       </c>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="C4" s="100"/>
@@ -8409,16 +8409,16 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="252" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="157" t="s">
+      <c r="B6" s="156" t="s">
         <v>478</v>
       </c>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="157"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="156"/>
+      <c r="I6" s="156"/>
     </row>
     <row r="8" spans="1:15" ht="36" x14ac:dyDescent="0.45">
       <c r="A8" s="86" t="s">
@@ -13154,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="s">
         <v>310</v>
@@ -17654,11 +17654,11 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="123.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="156" t="s">
         <v>519</v>
       </c>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
@@ -17666,11 +17666,11 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="121.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="157" t="s">
+      <c r="B7" s="156" t="s">
         <v>521</v>
       </c>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
     </row>
     <row r="9" spans="1:11" ht="36" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
@@ -17891,15 +17891,15 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="198" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="156" t="s">
         <v>588</v>
       </c>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
       <c r="I3" s="20"/>
     </row>
     <row r="5" spans="1:9" ht="36" x14ac:dyDescent="0.45">
@@ -17908,15 +17908,15 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="260" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="157" t="s">
+      <c r="B6" s="156" t="s">
         <v>513</v>
       </c>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="156"/>
       <c r="I6" s="20"/>
     </row>
     <row r="8" spans="1:9" ht="36" x14ac:dyDescent="0.45">
@@ -17926,15 +17926,15 @@
     </row>
     <row r="9" spans="1:9" ht="145.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14"/>
-      <c r="B9" s="157" t="s">
+      <c r="B9" s="156" t="s">
         <v>684</v>
       </c>
-      <c r="C9" s="157"/>
-      <c r="D9" s="157"/>
-      <c r="E9" s="157"/>
-      <c r="F9" s="157"/>
-      <c r="G9" s="157"/>
-      <c r="H9" s="157"/>
+      <c r="C9" s="156"/>
+      <c r="D9" s="156"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
+      <c r="H9" s="156"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B11" s="97" t="s">
@@ -18052,15 +18052,15 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="305.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="157" t="s">
+      <c r="B22" s="156" t="s">
         <v>535</v>
       </c>
-      <c r="C22" s="157"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="157"/>
-      <c r="H22" s="157"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="156"/>
+      <c r="G22" s="156"/>
+      <c r="H22" s="156"/>
       <c r="I22" s="20"/>
     </row>
     <row r="24" spans="1:19" ht="36" x14ac:dyDescent="0.45">
@@ -24915,15 +24915,15 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="321" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="156" t="s">
         <v>589</v>
       </c>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="1">
